--- a/ocr/test2.xlsx
+++ b/ocr/test2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,7 +620,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads services</t>
+          <t>Invoice for Meta ads</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads services</t>
+          <t>Invoice for Meta ads</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>['Ticket Restaurant', 'Ticket Compliments', 'MyBenefits']</t>
+          <t>['Ticket Restaurant', 'Ticket Compliments', 'MyBenefits', 'Spendeo', 'Spendeo Plus']</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -789,19 +789,19 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>{'Ticket Restaurant': 1049.3, 'Ticket Compliments': 0.0, 'MyBenefits': 0.0}</t>
+          <t>{'Ticket Restaurant': 1.0493, 'Ticket Compliments': 6.70529, 'MyBenefits': 5.24986, 'Spendeo': 4.17683, 'Spendeo Plus': 2.58474}</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>['1 Ιαν 2025 - 31 Ιαν 2025']</t>
+          <t>['01/01/2025 - 31/01/2025']</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VOUCHER SERVICES SA</t>
+          <t>Meta Platforms Ireland Limited</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,17 +812,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EL094438998</t>
+          <t>IE9692928F</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FBADS-266-104173647</t>
+          <t>FBADS-266-104152018</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26/01/2025</t>
+          <t>18/01/2025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Electronic Transfer</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -863,14 +863,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>EL094438998</t>
+          <t>IE9692928F</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>645.16</v>
+        <v>800</v>
       </c>
       <c r="Q4" t="n">
-        <v>154.84</v>
+        <v>0</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>['Ticket Restaurant', 'Spendeo']</t>
+          <t>['Spendeo', 'Ticket Restaurant']</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -903,12 +903,12 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>{'Ticket Restaurant': 749.47, 'Spendeo': 50.53}</t>
+          <t>{'Spendeo': 57.19, 'Ticket Restaurant': 742.81}</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['From 21/01/2025 to 26/01/2025']</t>
+          <t>['From 14/01/2025 to 18/01/2025']</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FBADS-266-104152018</t>
+          <t>FBADS-673-104093782</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18/01/2025</t>
+          <t>31/01/2025</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>800</v>
+        <v>524.62</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -962,12 +962,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads</t>
+          <t>Invoice for Myedenred.gr Account ID: 1013448069491872</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Electronic Transfer</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>800</v>
+        <v>524.62</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>['Spendeo', 'Ticket Restaurant']</t>
+          <t>['Ticket Restaurant', 'Ticket Compliments', 'Ticket Restaurant Paper', 'MyBenefits', 'Spendeo', 'Spendeo Plus']</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads</t>
+          <t>Invoice for Myedenred.gr Account ID: 1013448069491872</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>{'Spendeo': 57.19, 'Ticket Restaurant': 742.81}</t>
+          <t>{'Ticket Restaurant': 99.97, 'Ticket Compliments': 99.97, 'Ticket Restaurant Paper': 50.0, 'MyBenefits': 250.0, 'Spendeo': 75.08, 'Spendeo Plus': 49.57}</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['From 14/01/2025 to 18/01/2025']</t>
+          <t>['From 16/01/2025 to 30/01/2025', 'From 16/01/2025 to 30/01/2025', 'From 16/01/2025 to 30/01/2025', 'From 16/01/2025 to 30/01/2025', 'From 16/01/2025 to 30/01/2025', 'From 16/01/2025 to 30/01/2025']</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meta Platforms Ireland Limited</t>
+          <t>VOUCHER SERVICES SA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1040,17 +1040,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IE9692928F</t>
+          <t>EL094438998</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FBADS-673-104093782</t>
+          <t>FBADS-673-104054613</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>16/01/2025</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>524.62</v>
+        <v>800</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Invoice for Myedenred.gr Account ID: 1013448069491872</t>
+          <t>Invoice for Meta ads campaign</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>IE9692928F</t>
+          <t>EL094438998</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>524.62</v>
+        <v>645.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>154.84</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>['Ticket Restaurant', 'Ticket Compliments', 'Ticket Restaurant Paper', 'MyBenefits', 'Spendeo', 'Spendeo Plus']</t>
+          <t>['Ticket Restaurant']</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1125,25 +1125,25 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Invoice for Myedenred.gr Account ID: 1013448069491872</t>
+          <t>Invoice for Meta ads campaign</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>{'Meta ads': 524.62}</t>
+          <t>{'Ticket Restaurant': 800.0}</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>['From Jan 16, 2025, 12:00 AM to Jan 30, 2025, 11:59 PM']</t>
+          <t>['From 11/01/2025 to 16/01/2025', 'From 11/01/2025 to 16/01/2025']</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VOUCHER SERVICES SA</t>
+          <t>Meta Platforms Ireland Limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1154,17 +1154,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EL094438998</t>
+          <t>IE9692928F</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FBADS-673-104054613</t>
+          <t>FBADS-266-104187128</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16/01/2025</t>
+          <t>31/01/2025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>800</v>
+        <v>249.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads services</t>
+          <t>Invoice for Meta ads</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1205,14 +1205,14 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EL094438998</t>
+          <t>IE9692928F</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>645.16</v>
+        <v>249.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>154.84</v>
+        <v>0</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>['Ticket Restaurant']</t>
+          <t>['Ticket Restaurant', 'Spendeo']</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1239,25 +1239,25 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads services</t>
+          <t>Invoice for Meta ads</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>{'Ticket Restaurant': 800.0}</t>
+          <t>{'Ticket Restaurant': 230.88, 'Spendeo': 18.98}</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>['New Year Giveaway (2025) from 11/01/2025 to 16/01/2025', 'Όραμα καριέρας from 11/01/2025 to 16/01/2025']</t>
+          <t>['From Jan 28, 2025, 12:00 AM to Jan 30, 2025, 11:59 PM']</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VOUCHER SERVICES SA</t>
+          <t>Meta Platforms Ireland Limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1268,17 +1268,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EL094438998</t>
+          <t>IE9692928F</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FBADS-266-104187128</t>
+          <t>FBADS-266-104118246</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>249.86</v>
+        <v>800</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1319,14 +1319,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EL094438998</t>
+          <t>IE9692928F</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>201.5</v>
+        <v>800</v>
       </c>
       <c r="Q8" t="n">
-        <v>48.36</v>
+        <v>0</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -1359,12 +1359,12 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>{'Ticket Restaurant': 230.88, 'Spendeo': 18.98}</t>
+          <t>{'Ticket Restaurant': 743.48, 'Spendeo': 56.52}</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>['From 28/01/2025 to 30/01/2025', 'From 28/01/2025 to 30/01/2025']</t>
+          <t>['From 03/01/2025 to 07/01/2025']</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FBADS-266-104118246</t>
+          <t>FBADS-266-104182592</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>29/01/2025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>['Ticket Restaurant', 'Spendeo']</t>
+          <t>['Spendeo', 'Ticket Restaurant']</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1473,12 +1473,12 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>{'Ticket Restaurant': 743.48, 'Spendeo': 56.52}</t>
+          <t>{'Spendeo': 54.23, 'Ticket Restaurant': 745.77}</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>['From 03/01/2025 to 07/01/2025']</t>
+          <t>['From 25/01/2025 to 29/01/2025']</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FBADS-266-104182592</t>
+          <t>FBADS-266-104129980</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29/01/2025</t>
+          <t>11/01/2025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1587,12 +1587,12 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>{'Spendeo': 54.23, 'Ticket Restaurant': 745.77}</t>
+          <t>{'Spendeo': 54.15, 'Ticket Restaurant': 745.85}</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>['From 25/01/2025 to 29/01/2025']</t>
+          <t>['From 06/01/2025 to 11/01/2025']</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FBADS-266-104129980</t>
+          <t>FBADS-266-104108784</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads services</t>
+          <t>Invoice for Meta ads</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1695,18 +1695,18 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads services</t>
+          <t>Invoice for Meta ads</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>{'Spendeo': 54.15, 'Ticket Restaurant': 745.85}</t>
+          <t>{'Spendeo': 54.18, 'Ticket Restaurant': 745.82}</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>['From 06/01/2025 to 11/01/2025']</t>
+          <t>['From 30/12/2024 to 04/01/2025']</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FBADS-266-104108784</t>
+          <t>FBADS-673-104040892</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>12/01/2025</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>800</v>
+        <v>225.2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads</t>
+          <t>Invoice for Meta ads campaign</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>800</v>
+        <v>225.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>['Spendeo', 'Ticket Restaurant']</t>
+          <t>['Ticket Restaurant']</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1809,18 +1809,18 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads</t>
+          <t>Invoice for Meta ads campaign</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>{'Spendeo': 54.18, 'Ticket Restaurant': 745.82}</t>
+          <t>{'Ticket Restaurant': 225.2}</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>['From 30/12/2024 to 04/01/2025']</t>
+          <t>['From Jan 10, 2025, 12:00 AM to Jan 11, 2025, 11:59 PM']</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FBADS-673-104040892</t>
+          <t>FBADS-266-104162933</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
+          <t>22/01/2025</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>225.2</v>
+        <v>800</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads</t>
+          <t>Invoice for Meta ads services</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>225.2</v>
+        <v>800</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>['Ticket Restaurant']</t>
+          <t>['Spendeo', 'Ticket Restaurant']</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1923,130 +1923,16 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Invoice for Meta ads</t>
+          <t>Invoice for Meta ads services</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>{'Ticket Restaurant': 225.2}</t>
+          <t>{'Spendeo': 58.46, 'Ticket Restaurant': 741.54}</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
-        <is>
-          <t>['From Jan 10, 2025, 12:00 AM to Jan 11, 2025, 11:59 PM']</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Meta Platforms Ireland Limited</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>00709</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>IE9692928F</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>FBADS-266-104162933</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>22/01/2025</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>01/03/2025</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>800</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Invoice for Meta ads services</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Electronic Transfer</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>IE9692928F</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>800</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>['Spendeo', 'Ticket Restaurant']</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>0000</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Invoice for Meta ads services</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>{'Spendeo': 58.46, 'Ticket Restaurant': 741.54}</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
         <is>
           <t>['From 18/01/2025 to 22/01/2025']</t>
         </is>
